--- a/docs/paper_related/elements_arxml_count.xlsx
+++ b/docs/paper_related/elements_arxml_count.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习\科研\论文\CAD文章\20250806\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\39240\Desktop\tii\CodeGen4AUTOSAR-main\docs\paper_related\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B53A62-E340-4059-A878-1245BDA8D7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C94C6E-3354-4E9F-82EF-D231ED105D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="autosar_swc" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="autosar_swc_pedal_sensor" sheetId="5" r:id="rId5"/>
     <sheet name="autosar_swc_controller" sheetId="6" r:id="rId6"/>
     <sheet name="autosar_swc_actuator" sheetId="7" r:id="rId7"/>
+    <sheet name="large_scale_autosar_swc_expfcns" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="45">
   <si>
     <t>APPLICATION-SW-COMPONENT-TYPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2591,7 +2592,7 @@
         <v>43</v>
       </c>
       <c r="B16">
-        <f t="shared" ref="A16:D16" si="0">SUM(B2:B15)</f>
+        <f t="shared" ref="B16:D16" si="0">SUM(B2:B15)</f>
         <v>0</v>
       </c>
       <c r="C16">
@@ -2632,4 +2633,303 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348EC3CB-FDF3-4048-B1A4-9A86C15AC755}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.46484375" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14.9296875" customWidth="1"/>
+    <col min="4" max="4" width="28.3984375" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>211</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1">
+        <v>108</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
+        <v>109</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1">
+        <v>108</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1">
+        <v>331</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1">
+        <v>212</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1">
+        <v>115</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1">
+        <f>SUM(C2:C15)</f>
+        <v>1204</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1">
+        <f>SUM(E2:E15)</f>
+        <v>1198</v>
+      </c>
+      <c r="F16">
+        <f>E16/C16</f>
+        <v>0.99501661129568109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="1">
+        <v>14742</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10442</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A10"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>